--- a/daily_matches/job_matches_2026-06-20.xlsx
+++ b/daily_matches/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, Glue, Athena, Redshift, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, BigQuery, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372d6a67c10b163b</t>
+          <t>https://www.indeed.com/viewjob?jk=5760a4f1aa6fdddb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Associate, Site Reliability Engineering</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Athena, Docker, CI/CD, Terraform, Git, Databricks</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d58654d97d98c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hayden Industrial</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, FastAPI, Docker, Git, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26055662b5a07621</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Clinical Data Scientist</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rush University Medical Center</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, MySQL, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5455d44cb053bb0d</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Analyst</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Weston, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5bfcdfcaae8b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CSC</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Logan, UT, US USA</t>
+          <t>Kearney, NE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,392 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3d538cde897291</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer, Cloud and AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BEAR Cloud</t>
+          <t>ALLO Communications</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Grand Island, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Cloud and AI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ALLO Communications</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Commercial Analytics</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b528ce36c5db0190</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>^AI ML Engineer - 6352112</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Prompt Engineering, Azure ML, Azure ML Studio, Snowflake</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ebf057a00a5a0b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>^AI ML Engineer - 6352113</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Prompt Engineering, Azure ML, Azure ML Studio, Snowflake</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe5142a4eeb06d44</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shopify Architect</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer, Cat Digital Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Kinesis, CI/CD, GitHub Actions, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer (SMTS/LMTS) - Knowledge Graph &amp; AI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Copilot, Git, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ad48bb3932a9aa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Database Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Renovo Solutions</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d891b4246fa841</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e28407a214cbaca</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fabric Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Distinguished Engineer - AI Data Engine</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kubernetes, Dask, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4414785bc5726cba</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-20.xlsx
+++ b/daily_matches/job_matches_2026-06-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, BigQuery, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Dataflow, Docker, Kubernetes, Git, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5760a4f1aa6fdddb</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2d8e205af354cd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Data Engineer- Full Time Opportunity, NOT C2C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Apache Airflow, CI/CD, Git, PySpark, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,207 +531,207 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4bd1d0f1519ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=780ec295f6bacdf5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Databricks Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, MLflow, CI/CD, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf3f2dbb3812e475</t>
+          <t>https://www.indeed.com/viewjob?jk=f289865d551fa1a3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>RAG, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8ab90439d98b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1d97244cd7329e73</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Data Engineer, Quality Intelligence</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Databricks, PySpark, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6ecf773d8deb21</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ed17f3555e6cae</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Senior Snowflake Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kearney, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d8f5634d6f6d76</t>
+          <t>https://www.indeed.com/viewjob?jk=cf016976f76e7f0a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grand Island, NE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>RAG, S3, EC2, CI/CD, Snowflake, Databricks, PySpark, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ccaa9de6cb6d799</t>
+          <t>https://www.indeed.com/viewjob?jk=7758e2775271790b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud and AI</t>
+          <t>AI Researcher / ML Engineer (ASR &amp; Speech Specialist)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALLO Communications</t>
+          <t>Lilt- Lega Italiana per la Lotta contro i Tumori</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python</t>
+          <t>Machine Learning Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d6b37f8d80d085</t>
+          <t>https://www.indeed.com/viewjob?jk=12234e1fc4a78963</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist, Commercial Analytics</t>
+          <t>Quant Analytics Senior Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b528ce36c5db0190</t>
+          <t>https://www.indeed.com/viewjob?jk=3c187c33a4df15f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>^AI ML Engineer - 6352112</t>
+          <t>Fabric Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Prompt Engineering, Azure ML, Azure ML Studio, Snowflake</t>
+          <t>RAG, Synapse, Data Lake, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebf057a00a5a0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1831e001122e4d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>^AI ML Engineer - 6352113</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Attain Finance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Prompt Engineering, Azure ML, Azure ML Studio, Snowflake</t>
+          <t>RAG, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,217 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5142a4eeb06d44</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Shopify Architect</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc5601c059bd73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, Kinesis, CI/CD, GitHub Actions, Git, Snowflake, Python, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=826181dbe0e126ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Engineer (SMTS/LMTS) - Knowledge Graph &amp; AI</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Git, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ad48bb3932a9aa2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Database Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Renovo Solutions</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e28407a214cbaca</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fabric Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Data Lake, PySpark, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7b8660e24dfc38</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Distinguished Engineer - AI Data Engine</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, S3, Kubernetes, Dask, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4414785bc5726cba</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fd37f5d5683cc</t>
         </is>
       </c>
     </row>
